--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F8D762-38AC-41A1-8ECB-005B25D9075C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD1770-043F-4A71-87BE-51672C96DC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32835" yWindow="1815" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33375" yWindow="2220" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="261">
   <si>
     <t>SKU</t>
   </si>
@@ -220,195 +220,21 @@
     <t>Recticel Eurowall + Full-Fill Cavity 140mm x 1.2m x 0.46m (4.42m2) (4 P/Pal)</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?_pos=1&amp;_psq=REC25mm&amp;_ss=e&amp;_v=1.0&amp;variant=31766192783413</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192816181</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192848949</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192881717</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192914485</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192947253</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192980021</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766193012789</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766193045557</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192554037</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192586805</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192619573</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192652341</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192685109</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192717877</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31769668321333</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31769668452405</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31766306062389</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31766306095157</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=42960350609461</t>
-  </si>
-  <si>
     <t>£791.80</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733177909344</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733177942112</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733177974880</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178007648</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178040416</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178073184</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178105952</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178138720</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178171488</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178204256</t>
-  </si>
-  <si>
     <t>£48.66</t>
   </si>
   <si>
     <t>£49.35</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178302560</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178335328</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178368096</t>
-  </si>
-  <si>
     <t>POA</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31726714880096</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31726715011168</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31733114011744</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31733114044512</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31733114077280</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=47680288227521</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=47680288260289</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=47680288293057</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625999744</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626032512</t>
-  </si>
-  <si>
     <t>N/L</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626098048</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626130816</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626163584</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626196352</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626229120</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626261888</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625901440</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625934208</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625966976</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286930304</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286963072</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286995840</t>
-  </si>
-  <si>
     <t>£32.75</t>
   </si>
   <si>
@@ -565,12 +391,6 @@
     <t>£69.02</t>
   </si>
   <si>
-    <t>£141.19</t>
-  </si>
-  <si>
-    <t>£143.21</t>
-  </si>
-  <si>
     <t>£678.81</t>
   </si>
   <si>
@@ -622,51 +442,12 @@
     <t>£23.13</t>
   </si>
   <si>
-    <t>£19.27</t>
-  </si>
-  <si>
-    <t>£20.83</t>
-  </si>
-  <si>
-    <t>£24.26</t>
-  </si>
-  <si>
-    <t>£27.59</t>
-  </si>
-  <si>
-    <t>£31.06</t>
-  </si>
-  <si>
-    <t>£40.83</t>
-  </si>
-  <si>
-    <t>£43.06</t>
-  </si>
-  <si>
-    <t>£55.70</t>
-  </si>
-  <si>
-    <t>£74.88</t>
-  </si>
-  <si>
-    <t>£66.58</t>
-  </si>
-  <si>
-    <t>£78.08</t>
-  </si>
-  <si>
     <t>£126.96</t>
   </si>
   <si>
     <t>£122.43</t>
   </si>
   <si>
-    <t>£446.12</t>
-  </si>
-  <si>
-    <t>£356.90</t>
-  </si>
-  <si>
     <t>£15.25</t>
   </si>
   <si>
@@ -890,6 +671,138 @@
   </si>
   <si>
     <t>£57.57</t>
+  </si>
+  <si>
+    <t>£25.00</t>
+  </si>
+  <si>
+    <t>£29.11</t>
+  </si>
+  <si>
+    <t>£33.11</t>
+  </si>
+  <si>
+    <t>£37.27</t>
+  </si>
+  <si>
+    <t>£48.99</t>
+  </si>
+  <si>
+    <t>£51.67</t>
+  </si>
+  <si>
+    <t>£66.84</t>
+  </si>
+  <si>
+    <t>£79.89</t>
+  </si>
+  <si>
+    <t>£89.86</t>
+  </si>
+  <si>
+    <t>£93.69</t>
+  </si>
+  <si>
+    <t>£99.37</t>
+  </si>
+  <si>
+    <t>£657.00</t>
+  </si>
+  <si>
+    <t>£711.4</t>
+  </si>
+  <si>
+    <t>£17.75</t>
+  </si>
+  <si>
+    <t>£21.50</t>
+  </si>
+  <si>
+    <t>£23.25</t>
+  </si>
+  <si>
+    <t>£27.75</t>
+  </si>
+  <si>
+    <t>£31.50</t>
+  </si>
+  <si>
+    <t>£31.75</t>
+  </si>
+  <si>
+    <t>£35.25</t>
+  </si>
+  <si>
+    <t>£38.25</t>
+  </si>
+  <si>
+    <t>£39.75</t>
+  </si>
+  <si>
+    <t>£47.00</t>
+  </si>
+  <si>
+    <t>£48.75</t>
+  </si>
+  <si>
+    <t>£56.50</t>
+  </si>
+  <si>
+    <t>£59.75</t>
+  </si>
+  <si>
+    <t>£58.25</t>
+  </si>
+  <si>
+    <t>£17.84</t>
+  </si>
+  <si>
+    <t>£21.95</t>
+  </si>
+  <si>
+    <t>£29.55</t>
+  </si>
+  <si>
+    <t>£32.52</t>
+  </si>
+  <si>
+    <t>£36.18</t>
+  </si>
+  <si>
+    <t>£39.80</t>
+  </si>
+  <si>
+    <t>£58.94</t>
+  </si>
+  <si>
+    <t>£59.45</t>
+  </si>
+  <si>
+    <t>£126.47</t>
+  </si>
+  <si>
+    <t>£111.78</t>
+  </si>
+  <si>
+    <t>£41.50</t>
+  </si>
+  <si>
+    <t>£51.64</t>
+  </si>
+  <si>
+    <t>£55.32</t>
+  </si>
+  <si>
+    <t>£786.50</t>
+  </si>
+  <si>
+    <t>£276.59</t>
+  </si>
+  <si>
+    <t>£705.95</t>
+  </si>
+  <si>
+    <t>£716.05</t>
   </si>
 </sst>
 </file>
@@ -1324,52 +1237,52 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="F2" t="s">
-        <v>271</v>
+        <v>142</v>
       </c>
       <c r="G2" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="H2" t="s">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="I2" t="s">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="J2" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="K2" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="L2" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M2" t="s">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="N2" t="s">
-        <v>199</v>
+        <v>139</v>
       </c>
       <c r="O2" t="s">
-        <v>215</v>
+        <v>142</v>
       </c>
       <c r="P2" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q2" t="s">
-        <v>287</v>
+        <v>214</v>
       </c>
       <c r="R2" t="s">
-        <v>243</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1380,52 +1293,52 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
       <c r="F3" t="s">
-        <v>272</v>
+        <v>230</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="H3" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="J3" t="s">
-        <v>260</v>
+        <v>187</v>
       </c>
       <c r="K3" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="L3" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M3" t="s">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="N3" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="O3" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="P3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q3" t="s">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="R3" t="s">
-        <v>244</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1436,52 +1349,52 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>261</v>
+        <v>188</v>
       </c>
       <c r="K4" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="L4" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M4" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="N4" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="O4" t="s">
-        <v>217</v>
+        <v>144</v>
       </c>
       <c r="P4" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q4" t="s">
-        <v>273</v>
+        <v>200</v>
       </c>
       <c r="R4" t="s">
-        <v>245</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1492,52 +1405,52 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" t="s">
+        <v>103</v>
+      </c>
+      <c r="K5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L5" t="s">
+        <v>70</v>
+      </c>
+      <c r="M5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N5" t="s">
+        <v>219</v>
+      </c>
+      <c r="O5" t="s">
+        <v>145</v>
+      </c>
+      <c r="P5" t="s">
         <v>69</v>
       </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" t="s">
-        <v>133</v>
-      </c>
-      <c r="I5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J5" t="s">
-        <v>161</v>
-      </c>
-      <c r="K5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L5" t="s">
-        <v>116</v>
-      </c>
-      <c r="M5" t="s">
-        <v>187</v>
-      </c>
-      <c r="N5" t="s">
-        <v>202</v>
-      </c>
-      <c r="O5" t="s">
-        <v>218</v>
-      </c>
-      <c r="P5" t="s">
-        <v>105</v>
-      </c>
       <c r="Q5" t="s">
-        <v>236</v>
+        <v>163</v>
       </c>
       <c r="R5" t="s">
-        <v>246</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1548,52 +1461,52 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>246</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="E6" t="s">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="F6" t="s">
-        <v>275</v>
+        <v>233</v>
       </c>
       <c r="G6" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="H6" t="s">
-        <v>134</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="J6" t="s">
-        <v>262</v>
+        <v>189</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="L6" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M6" t="s">
-        <v>188</v>
+        <v>128</v>
       </c>
       <c r="N6" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="O6" t="s">
-        <v>219</v>
+        <v>146</v>
       </c>
       <c r="P6" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q6" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="R6" t="s">
-        <v>247</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1604,52 +1517,52 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="F7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G7" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="I7" t="s">
-        <v>151</v>
+        <v>93</v>
       </c>
       <c r="J7" t="s">
-        <v>263</v>
+        <v>190</v>
       </c>
       <c r="K7" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="L7" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M7" t="s">
-        <v>189</v>
+        <v>129</v>
       </c>
       <c r="N7" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>147</v>
       </c>
       <c r="P7" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q7" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="R7" t="s">
-        <v>248</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1660,52 +1573,52 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>71</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="J8" t="s">
-        <v>264</v>
+        <v>191</v>
       </c>
       <c r="K8" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="L8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M8" t="s">
-        <v>190</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="O8" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
       <c r="P8" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q8" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
       <c r="R8" t="s">
-        <v>249</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1716,52 +1629,52 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>248</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="E9" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="F9" t="s">
-        <v>276</v>
+        <v>236</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="J9" t="s">
-        <v>265</v>
+        <v>192</v>
       </c>
       <c r="K9" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="L9" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M9" t="s">
-        <v>191</v>
+        <v>131</v>
       </c>
       <c r="N9" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="O9" t="s">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="s">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="R9" t="s">
-        <v>250</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1772,52 +1685,52 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>249</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>249</v>
       </c>
       <c r="E10" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="F10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="H10" t="s">
-        <v>137</v>
+        <v>79</v>
       </c>
       <c r="I10" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="J10" t="s">
-        <v>266</v>
+        <v>193</v>
       </c>
       <c r="K10" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="L10" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M10" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N10" t="s">
-        <v>206</v>
+        <v>69</v>
       </c>
       <c r="O10" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q10" t="s">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="R10" t="s">
-        <v>251</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1828,52 +1741,52 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="D11" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="E11" t="s">
-        <v>123</v>
+        <v>204</v>
       </c>
       <c r="F11" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>204</v>
       </c>
       <c r="H11" t="s">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="J11" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="K11" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="L11" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M11" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="N11" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="O11" t="s">
-        <v>224</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q11" t="s">
-        <v>240</v>
+        <v>167</v>
       </c>
       <c r="R11" t="s">
-        <v>252</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1884,52 +1797,52 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="H12" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I12" t="s">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="J12" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="K12" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L12" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M12" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="N12" t="s">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="O12" t="s">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="P12" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q12" t="s">
-        <v>241</v>
+        <v>168</v>
       </c>
       <c r="R12" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
@@ -1940,52 +1853,52 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="G13" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="H13" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="J13" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="K13" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="L13" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M13" t="s">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="N13" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="O13" t="s">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="P13" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q13" t="s">
-        <v>278</v>
+        <v>205</v>
       </c>
       <c r="R13" t="s">
-        <v>253</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1996,52 +1909,52 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>250</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="E14" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>279</v>
+        <v>241</v>
       </c>
       <c r="G14" t="s">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="H14" t="s">
-        <v>140</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="J14" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="K14" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="L14" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M14" t="s">
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="N14" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="O14" t="s">
-        <v>227</v>
+        <v>154</v>
       </c>
       <c r="P14" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q14" t="s">
-        <v>242</v>
+        <v>169</v>
       </c>
       <c r="R14" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -2052,52 +1965,52 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>207</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>280</v>
+        <v>242</v>
       </c>
       <c r="G15" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="H15" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="J15" t="s">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="K15" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="L15" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M15" t="s">
-        <v>196</v>
+        <v>136</v>
       </c>
       <c r="N15" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="O15" t="s">
-        <v>228</v>
+        <v>155</v>
       </c>
       <c r="P15" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q15" t="s">
-        <v>288</v>
+        <v>215</v>
       </c>
       <c r="R15" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -2108,52 +2021,52 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>125</v>
+        <v>251</v>
       </c>
       <c r="F16" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="G16" t="s">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="H16" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="I16" t="s">
-        <v>159</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>268</v>
+        <v>195</v>
       </c>
       <c r="K16" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M16" t="s">
-        <v>197</v>
+        <v>137</v>
       </c>
       <c r="N16" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="O16" t="s">
-        <v>229</v>
+        <v>156</v>
       </c>
       <c r="P16" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q16" t="s">
-        <v>289</v>
+        <v>216</v>
       </c>
       <c r="R16" t="s">
-        <v>254</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2164,52 +2077,52 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="E17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="K17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="O17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="P17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="Q17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R17" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -2220,52 +2133,52 @@
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>252</v>
       </c>
       <c r="E18" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>282</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="H18" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I18" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J18" t="s">
-        <v>269</v>
+        <v>196</v>
       </c>
       <c r="K18" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L18" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M18" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N18" t="s">
-        <v>211</v>
+        <v>140</v>
       </c>
       <c r="O18" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="P18" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q18" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R18" t="s">
-        <v>255</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2276,52 +2189,52 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>253</v>
       </c>
       <c r="E19" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>283</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>210</v>
       </c>
       <c r="H19" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I19" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J19" t="s">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="K19" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M19" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N19" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="O19" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="P19" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="Q19" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R19" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2332,52 +2245,52 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>254</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="H20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J20" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="K20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="O20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="P20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="Q20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R20" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -2388,52 +2301,52 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>255</v>
       </c>
       <c r="E21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J21" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="K21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="O21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="P21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="Q21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R21" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -2444,52 +2357,52 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="H22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="I22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J22" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="K22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="L22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="N22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="O22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="P22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="Q22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R22" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -2500,52 +2413,52 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>257</v>
       </c>
       <c r="E23" t="s">
-        <v>126</v>
+        <v>257</v>
       </c>
       <c r="F23" t="s">
-        <v>284</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="H23" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="I23" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J23" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="K23" t="s">
-        <v>181</v>
+        <v>259</v>
       </c>
       <c r="L23" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M23" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="N23" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="O23" t="s">
-        <v>232</v>
+        <v>159</v>
       </c>
       <c r="P23" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="Q23" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R23" t="s">
-        <v>257</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2556,52 +2469,52 @@
         <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>257</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>257</v>
       </c>
       <c r="E24" t="s">
-        <v>127</v>
+        <v>257</v>
       </c>
       <c r="F24" t="s">
-        <v>285</v>
+        <v>70</v>
       </c>
       <c r="G24" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="H24" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J24" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="K24" t="s">
-        <v>182</v>
+        <v>260</v>
       </c>
       <c r="L24" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M24" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="N24" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="O24" t="s">
-        <v>233</v>
+        <v>160</v>
       </c>
       <c r="P24" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="Q24" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R24" t="s">
-        <v>258</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2612,52 +2525,52 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="E25" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>286</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="H25" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="I25" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="J25" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="K25" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="L25" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="M25" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="N25" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="O25" t="s">
-        <v>234</v>
+        <v>161</v>
       </c>
       <c r="P25" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="R25" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD1770-043F-4A71-87BE-51672C96DC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33375" yWindow="2220" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="287">
   <si>
     <t>SKU</t>
   </si>
@@ -220,234 +214,542 @@
     <t>Recticel Eurowall + Full-Fill Cavity 140mm x 1.2m x 0.46m (4.42m2) (4 P/Pal)</t>
   </si>
   <si>
-    <t>£791.80</t>
-  </si>
-  <si>
-    <t>£48.66</t>
-  </si>
-  <si>
-    <t>£49.35</t>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?_pos=1&amp;_psq=REC25mm&amp;_ss=e&amp;_v=1.0&amp;variant=31766192783413</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192816181</t>
+  </si>
+  <si>
+    <t>£21.95</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192881717</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192914485</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192947253</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192980021</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766193012789</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766193045557</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192554037</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192586805</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192619573</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192652341</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192685109</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192717877</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31769668321333</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31769668452405</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31766306062389</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31766306095157</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=42960350609461</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=42960350642229</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes.json</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes.json</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes.json</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurowall-full-fill-cavity.json</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625999744</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626032512</t>
+  </si>
+  <si>
+    <t>N/L</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626098048</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626130816</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626163584</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626196352</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626229120</t>
+  </si>
+  <si>
+    <t>£39.80</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625901440</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625934208</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625966976</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286930304</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286963072</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286995840</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-25mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-30mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-40mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-50mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-60mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-70mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-75mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-80mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-90mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-100mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-110mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-120mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-130mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-140mm.html</t>
+  </si>
+  <si>
+    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-150mm.html</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/25mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/30mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/40mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/50mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/60mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/70mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/75mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/80mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/90mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/100mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/110mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/120mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/130mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/140mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/150mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/50mm-recticel-eurowall-partial-fill-cavity-insulation-board-1200mm-x-450mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/100mm-recticel-eurowall-partial-fill-cavity-insulation-board-1200mm-x-450mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/90mm-recticel-eurowall-full-fill-cavity-wall-insulation-1200mm-x-460mm</t>
+  </si>
+  <si>
+    <t>£703.35</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/140mm-recticel-eurowall-full-fill-cavity-wall-insulation-1200mm-x-460mm</t>
+  </si>
+  <si>
+    <t>£15.38</t>
+  </si>
+  <si>
+    <t>£18.02</t>
+  </si>
+  <si>
+    <t>£22.30</t>
+  </si>
+  <si>
+    <t>£23.32</t>
+  </si>
+  <si>
+    <t>£29.95</t>
+  </si>
+  <si>
+    <t>£32.88</t>
+  </si>
+  <si>
+    <t>£36.59</t>
+  </si>
+  <si>
+    <t>£40.25</t>
+  </si>
+  <si>
+    <t>£39.77</t>
+  </si>
+  <si>
+    <t>£49.40</t>
+  </si>
+  <si>
+    <t>£59.43</t>
+  </si>
+  <si>
+    <t>£60.43</t>
+  </si>
+  <si>
+    <t>£59.53</t>
+  </si>
+  <si>
+    <t>£582.95</t>
+  </si>
+  <si>
+    <t>£660.75</t>
+  </si>
+  <si>
+    <t>£561.2</t>
+  </si>
+  <si>
+    <t>£15.52</t>
+  </si>
+  <si>
+    <t>£20.00</t>
+  </si>
+  <si>
+    <t>£23.69</t>
+  </si>
+  <si>
+    <t>£23.57</t>
+  </si>
+  <si>
+    <t>£31.04</t>
+  </si>
+  <si>
+    <t>£35.31</t>
+  </si>
+  <si>
+    <t>£35.53</t>
+  </si>
+  <si>
+    <t>£40.65</t>
+  </si>
+  <si>
+    <t>£44.57</t>
+  </si>
+  <si>
+    <t>£38.33</t>
+  </si>
+  <si>
+    <t>£58.88</t>
+  </si>
+  <si>
+    <t>£50.59</t>
+  </si>
+  <si>
+    <t>£63.71</t>
+  </si>
+  <si>
+    <t>£67.28</t>
+  </si>
+  <si>
+    <t>£62.09</t>
+  </si>
+  <si>
+    <t>£22.54</t>
+  </si>
+  <si>
+    <t>£26.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (457, 837). Other element would receive the click: &lt;button type="button" class="btn btn-primary gap-2" data-role="cta"&gt;...&lt;/button&gt;
+  (Session info: chrome=150.0.7871.187); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff6e05a0d25+155a5]
+	chromedriver!GetHandleVerifier [0x7ff6e05a0d80+15600]
+	chromedriver!(No symbol) [0x7ff6e00f594d]
+	chromedriver!(No symbol) [0x7ff6e0158575]
+	chromedriver!(No symbol) [0x7ff6e0156193]
+	chromedriver!(No symbol) [0x7ff6e01534e7]
+	chromedriver!(No symbol) [0x7ff6e01523a0]
+	chromedriver!(No symbol) [0x7ff6e0144d98]
+	chromedriver!(No symbol) [0x7ff6e01791ca]
+	chromedriver!(No symbol) [0x7ff6e0144616]
+	chromedriver!(No symbol) [0x7ff6e019e01b]
+	chromedriver!(No symbol) [0x7ff6e0142e6c]
+	chromedriver!(No symbol) [0x7ff6e0143d93]
+	chromedriver!GetHandleVerifier [0x7ff6e0b86431+5facb1]
+	chromedriver!GetHandleVerifier [0x7ff6e0b80a9b+5f531b]
+	chromedriver!GetHandleVerifier [0x7ff6e0ba5865+61a0e5]
+	chromedriver!GetHandleVerifier [0x7ff6e05bdace+3234e]
+	chromedriver!GetHandleVerifier [0x7ff6e05c661c+3ae9c]
+	chromedriver!GetHandleVerifier [0x7ff6e05aab74+1f3f4]
+	chromedriver!GetHandleVerifier [0x7ff6e05aad04+1f584]
+	chromedriver!GetHandleVerifier [0x7ff6e058d9d7+2257]
+	KERNEL32!BaseThreadInitThunk [0x7ffe9eb7e957+17]
+	ntdll!RtlUserThreadStart [0x7ffea0ecad6c+2c]
+</t>
+  </si>
+  <si>
+    <t>£36.62</t>
+  </si>
+  <si>
+    <t>£43.70</t>
+  </si>
+  <si>
+    <t>£47.75</t>
+  </si>
+  <si>
+    <t>£58.84</t>
+  </si>
+  <si>
+    <t>£61.51</t>
+  </si>
+  <si>
+    <t>£70.54</t>
+  </si>
+  <si>
+    <t>£89.03</t>
+  </si>
+  <si>
+    <t>£77.15</t>
+  </si>
+  <si>
+    <t>£138.11</t>
+  </si>
+  <si>
+    <t>£129.92</t>
+  </si>
+  <si>
+    <t>£17.64</t>
+  </si>
+  <si>
+    <t>£21.06</t>
+  </si>
+  <si>
+    <t>£24.55</t>
+  </si>
+  <si>
+    <t>£27.69</t>
+  </si>
+  <si>
+    <t>£33.07</t>
+  </si>
+  <si>
+    <t>£37.17</t>
+  </si>
+  <si>
+    <t>£38.54</t>
+  </si>
+  <si>
+    <t>£42.71</t>
+  </si>
+  <si>
+    <t>£46.54</t>
+  </si>
+  <si>
+    <t>£57.45</t>
+  </si>
+  <si>
+    <t>£66.29</t>
+  </si>
+  <si>
+    <t>£67.50</t>
+  </si>
+  <si>
+    <t>£69.02</t>
+  </si>
+  <si>
+    <t>£141.19</t>
+  </si>
+  <si>
+    <t>£143.21</t>
+  </si>
+  <si>
+    <t>£678.81</t>
+  </si>
+  <si>
+    <t>£17.32</t>
+  </si>
+  <si>
+    <t>£21.10</t>
+  </si>
+  <si>
+    <t>£25.04</t>
+  </si>
+  <si>
+    <t>£26.34</t>
+  </si>
+  <si>
+    <t>£31.92</t>
+  </si>
+  <si>
+    <t>£33.06</t>
+  </si>
+  <si>
+    <t>£36.51</t>
+  </si>
+  <si>
+    <t>£40.31</t>
+  </si>
+  <si>
+    <t>£45.66</t>
+  </si>
+  <si>
+    <t>£102.12</t>
+  </si>
+  <si>
+    <t>£54.05</t>
+  </si>
+  <si>
+    <t>£63.05</t>
+  </si>
+  <si>
+    <t>£65.55</t>
+  </si>
+  <si>
+    <t>£66.70</t>
+  </si>
+  <si>
+    <t>£836.5</t>
   </si>
   <si>
     <t>POA</t>
   </si>
   <si>
-    <t>N/L</t>
-  </si>
-  <si>
-    <t>£32.75</t>
-  </si>
-  <si>
-    <t>£15.38</t>
-  </si>
-  <si>
-    <t>£18.02</t>
-  </si>
-  <si>
-    <t>£22.30</t>
-  </si>
-  <si>
-    <t>£23.32</t>
-  </si>
-  <si>
-    <t>£29.95</t>
-  </si>
-  <si>
-    <t>£32.88</t>
-  </si>
-  <si>
-    <t>£36.59</t>
-  </si>
-  <si>
-    <t>£40.25</t>
-  </si>
-  <si>
-    <t>£39.77</t>
-  </si>
-  <si>
-    <t>£49.40</t>
-  </si>
-  <si>
-    <t>£59.43</t>
-  </si>
-  <si>
-    <t>£60.43</t>
-  </si>
-  <si>
-    <t>£59.53</t>
-  </si>
-  <si>
-    <t>£582.95</t>
-  </si>
-  <si>
-    <t>£660.75</t>
-  </si>
-  <si>
-    <t>£561.2</t>
-  </si>
-  <si>
-    <t>£15.52</t>
-  </si>
-  <si>
-    <t>£20.00</t>
-  </si>
-  <si>
-    <t>£23.69</t>
-  </si>
-  <si>
-    <t>£23.57</t>
-  </si>
-  <si>
-    <t>£31.04</t>
-  </si>
-  <si>
-    <t>£35.31</t>
-  </si>
-  <si>
-    <t>£40.65</t>
-  </si>
-  <si>
-    <t>£44.57</t>
-  </si>
-  <si>
-    <t>£38.33</t>
-  </si>
-  <si>
-    <t>£58.88</t>
-  </si>
-  <si>
-    <t>£50.59</t>
-  </si>
-  <si>
-    <t>£63.71</t>
-  </si>
-  <si>
-    <t>£67.28</t>
-  </si>
-  <si>
-    <t>£62.09</t>
-  </si>
-  <si>
-    <t>£22.54</t>
-  </si>
-  <si>
-    <t>£36.62</t>
-  </si>
-  <si>
-    <t>£70.54</t>
-  </si>
-  <si>
-    <t>£72.71</t>
-  </si>
-  <si>
-    <t>£83.24</t>
-  </si>
-  <si>
-    <t>£101.46</t>
-  </si>
-  <si>
-    <t>£114.31</t>
-  </si>
-  <si>
-    <t>£129.92</t>
-  </si>
-  <si>
-    <t>£17.64</t>
-  </si>
-  <si>
-    <t>£21.06</t>
-  </si>
-  <si>
-    <t>£24.55</t>
-  </si>
-  <si>
-    <t>£27.69</t>
-  </si>
-  <si>
-    <t>£33.07</t>
-  </si>
-  <si>
-    <t>£37.17</t>
-  </si>
-  <si>
-    <t>£38.54</t>
-  </si>
-  <si>
-    <t>£42.71</t>
-  </si>
-  <si>
-    <t>£46.54</t>
-  </si>
-  <si>
-    <t>£57.45</t>
-  </si>
-  <si>
-    <t>£66.29</t>
-  </si>
-  <si>
-    <t>£67.50</t>
-  </si>
-  <si>
-    <t>£69.02</t>
-  </si>
-  <si>
-    <t>£678.81</t>
-  </si>
-  <si>
-    <t>£17.32</t>
-  </si>
-  <si>
-    <t>£21.10</t>
-  </si>
-  <si>
-    <t>£25.04</t>
-  </si>
-  <si>
-    <t>£26.34</t>
-  </si>
-  <si>
-    <t>£31.92</t>
-  </si>
-  <si>
-    <t>£33.06</t>
-  </si>
-  <si>
-    <t>£36.51</t>
-  </si>
-  <si>
-    <t>£40.31</t>
-  </si>
-  <si>
-    <t>£45.66</t>
-  </si>
-  <si>
-    <t>£102.12</t>
-  </si>
-  <si>
-    <t>£54.05</t>
-  </si>
-  <si>
-    <t>£63.05</t>
-  </si>
-  <si>
-    <t>£65.55</t>
-  </si>
-  <si>
-    <t>£66.70</t>
-  </si>
-  <si>
-    <t>£836.5</t>
-  </si>
-  <si>
     <t>£23.13</t>
   </si>
   <si>
+    <t>£19.27</t>
+  </si>
+  <si>
+    <t>£20.83</t>
+  </si>
+  <si>
+    <t>£24.26</t>
+  </si>
+  <si>
+    <t>£27.59</t>
+  </si>
+  <si>
+    <t>£31.06</t>
+  </si>
+  <si>
+    <t>£40.83</t>
+  </si>
+  <si>
+    <t>£43.06</t>
+  </si>
+  <si>
+    <t>£55.70</t>
+  </si>
+  <si>
+    <t>£74.88</t>
+  </si>
+  <si>
+    <t>£66.58</t>
+  </si>
+  <si>
+    <t>£78.08</t>
+  </si>
+  <si>
     <t>£126.96</t>
   </si>
   <si>
     <t>£122.43</t>
   </si>
   <si>
+    <t>£446.12</t>
+  </si>
+  <si>
+    <t>£356.90</t>
+  </si>
+  <si>
     <t>£15.25</t>
   </si>
   <si>
@@ -508,12 +810,21 @@
     <t>£559.96</t>
   </si>
   <si>
+    <t>£15.17</t>
+  </si>
+  <si>
     <t>£18.31</t>
   </si>
   <si>
+    <t>£21.43</t>
+  </si>
+  <si>
     <t>£23.45</t>
   </si>
   <si>
+    <t>£28.83</t>
+  </si>
+  <si>
     <t>£32.44</t>
   </si>
   <si>
@@ -529,287 +840,74 @@
     <t>£48.84</t>
   </si>
   <si>
+    <t>£49.31</t>
+  </si>
+  <si>
     <t>£56.17</t>
   </si>
   <si>
-    <t>£16.67</t>
-  </si>
-  <si>
-    <t>£19.49</t>
-  </si>
-  <si>
-    <t>£24.85</t>
-  </si>
-  <si>
-    <t>£25.82</t>
-  </si>
-  <si>
-    <t>£31.54</t>
-  </si>
-  <si>
-    <t>£36.34</t>
-  </si>
-  <si>
-    <t>£35.03</t>
-  </si>
-  <si>
-    <t>£39.38</t>
-  </si>
-  <si>
-    <t>£44.47</t>
-  </si>
-  <si>
-    <t>£43.77</t>
-  </si>
-  <si>
-    <t>£54.40</t>
-  </si>
-  <si>
-    <t>£66.42</t>
-  </si>
-  <si>
-    <t>£117.43</t>
-  </si>
-  <si>
-    <t>£203.51</t>
-  </si>
-  <si>
-    <t>£848.7</t>
-  </si>
-  <si>
-    <t>£908.35</t>
-  </si>
-  <si>
-    <t>£1156.54</t>
-  </si>
-  <si>
-    <t>£26.28</t>
-  </si>
-  <si>
-    <t>£31.96</t>
-  </si>
-  <si>
-    <t>£43.70</t>
-  </si>
-  <si>
-    <t>£47.75</t>
-  </si>
-  <si>
-    <t>£48.18</t>
-  </si>
-  <si>
-    <t>£58.84</t>
-  </si>
-  <si>
-    <t>£61.51</t>
-  </si>
-  <si>
-    <t>£89.03</t>
-  </si>
-  <si>
-    <t>£90.28</t>
-  </si>
-  <si>
-    <t>£77.15</t>
-  </si>
-  <si>
-    <t>£138.11</t>
-  </si>
-  <si>
-    <t>£15.50</t>
-  </si>
-  <si>
-    <t>£17.99</t>
-  </si>
-  <si>
-    <t>£21.43</t>
-  </si>
-  <si>
-    <t>£23.15</t>
-  </si>
-  <si>
-    <t>£28.83</t>
-  </si>
-  <si>
-    <t>£36.45</t>
-  </si>
-  <si>
-    <t>£39.65</t>
-  </si>
-  <si>
-    <t>£49.31</t>
-  </si>
-  <si>
-    <t>£59.02</t>
-  </si>
-  <si>
-    <t>£59.99</t>
-  </si>
-  <si>
-    <t>£58.97</t>
-  </si>
-  <si>
-    <t>£206.12</t>
-  </si>
-  <si>
-    <t>£182.51</t>
-  </si>
-  <si>
-    <t>£626.65</t>
-  </si>
-  <si>
-    <t>£703.35</t>
-  </si>
-  <si>
-    <t>£728.0</t>
-  </si>
-  <si>
-    <t>£15.17</t>
-  </si>
-  <si>
-    <t>£58.05</t>
+    <t>£57.15</t>
   </si>
   <si>
     <t>£57.57</t>
   </si>
   <si>
-    <t>£25.00</t>
-  </si>
-  <si>
-    <t>£29.11</t>
-  </si>
-  <si>
-    <t>£33.11</t>
-  </si>
-  <si>
-    <t>£37.27</t>
-  </si>
-  <si>
-    <t>£48.99</t>
-  </si>
-  <si>
-    <t>£51.67</t>
-  </si>
-  <si>
-    <t>£66.84</t>
-  </si>
-  <si>
-    <t>£79.89</t>
-  </si>
-  <si>
-    <t>£89.86</t>
-  </si>
-  <si>
-    <t>£93.69</t>
-  </si>
-  <si>
-    <t>£99.37</t>
-  </si>
-  <si>
-    <t>£657.00</t>
-  </si>
-  <si>
-    <t>£711.4</t>
-  </si>
-  <si>
-    <t>£17.75</t>
-  </si>
-  <si>
-    <t>£21.50</t>
-  </si>
-  <si>
-    <t>£23.25</t>
-  </si>
-  <si>
-    <t>£27.75</t>
-  </si>
-  <si>
-    <t>£31.50</t>
-  </si>
-  <si>
-    <t>£31.75</t>
-  </si>
-  <si>
-    <t>£35.25</t>
-  </si>
-  <si>
-    <t>£38.25</t>
-  </si>
-  <si>
-    <t>£39.75</t>
-  </si>
-  <si>
-    <t>£47.00</t>
-  </si>
-  <si>
-    <t>£48.75</t>
-  </si>
-  <si>
-    <t>£56.50</t>
-  </si>
-  <si>
-    <t>£59.75</t>
-  </si>
-  <si>
-    <t>£58.25</t>
-  </si>
-  <si>
-    <t>£17.84</t>
-  </si>
-  <si>
-    <t>£21.95</t>
-  </si>
-  <si>
-    <t>£29.55</t>
-  </si>
-  <si>
-    <t>£32.52</t>
-  </si>
-  <si>
-    <t>£36.18</t>
-  </si>
-  <si>
-    <t>£39.80</t>
-  </si>
-  <si>
-    <t>£58.94</t>
-  </si>
-  <si>
-    <t>£59.45</t>
-  </si>
-  <si>
-    <t>£126.47</t>
-  </si>
-  <si>
-    <t>£111.78</t>
-  </si>
-  <si>
-    <t>£41.50</t>
-  </si>
-  <si>
-    <t>£51.64</t>
-  </si>
-  <si>
-    <t>£55.32</t>
-  </si>
-  <si>
-    <t>£786.50</t>
-  </si>
-  <si>
-    <t>£276.59</t>
-  </si>
-  <si>
-    <t>£705.95</t>
-  </si>
-  <si>
-    <t>£716.05</t>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/25mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/30mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/40mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/50mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/60mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/70mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/75mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/80mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/90mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/100mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/120mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/150mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/50mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/100mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/90mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/115mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
+  </si>
+  <si>
+    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/140mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -872,21 +970,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -924,7 +1014,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -958,7 +1048,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -993,10 +1082,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1169,11 +1257,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1229,7 +1317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1237,55 +1325,55 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>124</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s">
-        <v>88</v>
+        <v>160</v>
       </c>
       <c r="J2" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="K2" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="L2" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M2" t="s">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="N2" t="s">
-        <v>139</v>
+        <v>220</v>
       </c>
       <c r="O2" t="s">
-        <v>142</v>
+        <v>236</v>
       </c>
       <c r="P2" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q2" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="R2" t="s">
-        <v>170</v>
+        <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1293,55 +1381,55 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>244</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>244</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>244</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="G3" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="I3" t="s">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="J3" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="K3" t="s">
-        <v>111</v>
+        <v>189</v>
       </c>
       <c r="L3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s">
-        <v>125</v>
+        <v>205</v>
       </c>
       <c r="N3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="O3" t="s">
-        <v>143</v>
+        <v>237</v>
       </c>
       <c r="P3" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q3" t="s">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="R3" t="s">
-        <v>171</v>
+        <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1349,55 +1437,55 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F4" t="s">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="G4" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="H4" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
       <c r="J4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="K4" t="s">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="L4" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="N4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="O4" t="s">
-        <v>144</v>
+        <v>238</v>
       </c>
       <c r="P4" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q4" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="R4" t="s">
-        <v>172</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1405,55 +1493,55 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>201</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="F5" t="s">
-        <v>232</v>
+        <v>112</v>
       </c>
       <c r="G5" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="I5" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>178</v>
       </c>
       <c r="K5" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="L5" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M5" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="N5" t="s">
+        <v>223</v>
+      </c>
+      <c r="O5" t="s">
+        <v>239</v>
+      </c>
+      <c r="P5" t="s">
         <v>219</v>
       </c>
-      <c r="O5" t="s">
-        <v>145</v>
-      </c>
-      <c r="P5" t="s">
-        <v>69</v>
-      </c>
       <c r="Q5" t="s">
-        <v>163</v>
+        <v>259</v>
       </c>
       <c r="R5" t="s">
-        <v>173</v>
+        <v>273</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1461,55 +1549,55 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>246</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>246</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>246</v>
+        <v>98</v>
       </c>
       <c r="F6" t="s">
-        <v>233</v>
+        <v>113</v>
       </c>
       <c r="G6" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="H6" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="I6" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="J6" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="K6" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="L6" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M6" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="N6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="P6" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q6" t="s">
-        <v>202</v>
+        <v>260</v>
       </c>
       <c r="R6" t="s">
-        <v>174</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1517,55 +1605,55 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>247</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>247</v>
+        <v>99</v>
       </c>
       <c r="F7" t="s">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="G7" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="I7" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="J7" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="K7" t="s">
-        <v>115</v>
+        <v>193</v>
       </c>
       <c r="L7" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="N7" t="s">
-        <v>69</v>
+        <v>225</v>
       </c>
       <c r="O7" t="s">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="P7" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q7" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="R7" t="s">
-        <v>175</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1573,55 +1661,55 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="I8" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="J8" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="K8" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="L8" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="N8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="O8" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="P8" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q8" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="R8" t="s">
-        <v>176</v>
+        <v>276</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1629,55 +1717,55 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>248</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>248</v>
+        <v>101</v>
       </c>
       <c r="F9" t="s">
-        <v>236</v>
+        <v>116</v>
       </c>
       <c r="G9" t="s">
-        <v>203</v>
+        <v>131</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>167</v>
       </c>
       <c r="J9" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="K9" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="L9" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M9" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="N9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="O9" t="s">
-        <v>149</v>
+        <v>243</v>
       </c>
       <c r="P9" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q9" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="R9" t="s">
-        <v>177</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1685,55 +1773,55 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>249</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>249</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>237</v>
+        <v>117</v>
       </c>
       <c r="G10" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="H10" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="I10" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="J10" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="K10" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="L10" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M10" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="N10" t="s">
-        <v>69</v>
+        <v>227</v>
       </c>
       <c r="O10" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="P10" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q10" t="s">
-        <v>166</v>
+        <v>263</v>
       </c>
       <c r="R10" t="s">
-        <v>178</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1741,55 +1829,55 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="F11" t="s">
-        <v>238</v>
+        <v>118</v>
       </c>
       <c r="G11" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="I11" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="J11" t="s">
-        <v>104</v>
+        <v>183</v>
       </c>
       <c r="K11" t="s">
-        <v>118</v>
+        <v>196</v>
       </c>
       <c r="L11" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M11" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="N11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="O11" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="P11" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="R11" t="s">
-        <v>179</v>
+        <v>279</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1797,55 +1885,55 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F12" t="s">
-        <v>239</v>
+        <v>119</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="H12" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I12" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="J12" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L12" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M12" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="N12" t="s">
-        <v>69</v>
+        <v>228</v>
       </c>
       <c r="O12" t="s">
-        <v>152</v>
+        <v>246</v>
       </c>
       <c r="P12" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q12" t="s">
-        <v>168</v>
+        <v>265</v>
       </c>
       <c r="R12" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1853,55 +1941,55 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="F13" t="s">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="G13" t="s">
-        <v>205</v>
+        <v>135</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c r="I13" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="J13" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="K13" t="s">
-        <v>119</v>
+        <v>197</v>
       </c>
       <c r="L13" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M13" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="N13" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="O13" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="P13" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q13" t="s">
-        <v>205</v>
+        <v>266</v>
       </c>
       <c r="R13" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1909,55 +1997,55 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="G14" t="s">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="H14" t="s">
-        <v>82</v>
+        <v>154</v>
       </c>
       <c r="I14" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="K14" t="s">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="L14" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M14" t="s">
-        <v>135</v>
+        <v>215</v>
       </c>
       <c r="N14" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="O14" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="P14" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q14" t="s">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="R14" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1965,55 +2053,55 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F15" t="s">
-        <v>242</v>
+        <v>122</v>
       </c>
       <c r="G15" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>155</v>
       </c>
       <c r="I15" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="J15" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="K15" t="s">
-        <v>121</v>
+        <v>199</v>
       </c>
       <c r="L15" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M15" t="s">
-        <v>136</v>
+        <v>216</v>
       </c>
       <c r="N15" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="O15" t="s">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="P15" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q15" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="R15" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2021,55 +2109,55 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>251</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="F16" t="s">
-        <v>243</v>
+        <v>123</v>
       </c>
       <c r="G16" t="s">
-        <v>208</v>
+        <v>138</v>
       </c>
       <c r="H16" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="K16" t="s">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="L16" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M16" t="s">
-        <v>137</v>
+        <v>217</v>
       </c>
       <c r="N16" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="O16" t="s">
-        <v>156</v>
+        <v>250</v>
       </c>
       <c r="P16" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q16" t="s">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="R16" t="s">
-        <v>181</v>
+        <v>281</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2077,55 +2165,55 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>258</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="N17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="O17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="Q17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R17" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2133,55 +2221,55 @@
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>252</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G18" t="s">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="H18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J18" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="K18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="N18" t="s">
-        <v>140</v>
+        <v>232</v>
       </c>
       <c r="O18" t="s">
-        <v>157</v>
+        <v>251</v>
       </c>
       <c r="P18" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q18" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R18" t="s">
-        <v>182</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2189,55 +2277,55 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>253</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G19" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="H19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J19" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="K19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="N19" t="s">
-        <v>141</v>
+        <v>233</v>
       </c>
       <c r="O19" t="s">
-        <v>158</v>
+        <v>252</v>
       </c>
       <c r="P19" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="Q19" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R19" t="s">
-        <v>183</v>
+        <v>283</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2245,55 +2333,55 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>254</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J20" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="K20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="N20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="O20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="Q20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R20" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2301,55 +2389,55 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>255</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J21" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="K21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="N21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="O21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="Q21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R21" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2357,55 +2445,55 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>256</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>256</v>
+        <v>92</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="H22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="I22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J22" t="s">
-        <v>109</v>
+        <v>187</v>
       </c>
       <c r="K22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="N22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="O22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="P22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="Q22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R22" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2413,55 +2501,55 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G23" t="s">
-        <v>211</v>
+        <v>141</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="I23" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J23" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="K23" t="s">
-        <v>259</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M23" t="s">
-        <v>138</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O23" t="s">
-        <v>159</v>
+        <v>253</v>
       </c>
       <c r="P23" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="Q23" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R23" t="s">
-        <v>184</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2469,55 +2557,55 @@
         <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>257</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>257</v>
+        <v>107</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
-        <v>212</v>
+        <v>142</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="I24" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s">
-        <v>260</v>
+        <v>202</v>
       </c>
       <c r="L24" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M24" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="N24" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="O24" t="s">
-        <v>160</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="Q24" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R24" t="s">
-        <v>185</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2525,52 +2613,52 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>143</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="I25" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="J25" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="K25" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="L25" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="M25" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="N25" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="O25" t="s">
-        <v>161</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="Q25" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R25" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286A6C96-0363-495F-A2B2-213AC530EB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="33870" yWindow="1710" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="262">
   <si>
     <t>SKU</t>
   </si>
@@ -214,240 +220,18 @@
     <t>Recticel Eurowall + Full-Fill Cavity 140mm x 1.2m x 0.46m (4.42m2) (4 P/Pal)</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?_pos=1&amp;_psq=REC25mm&amp;_ss=e&amp;_v=1.0&amp;variant=31766192783413</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192816181</t>
-  </si>
-  <si>
     <t>£21.95</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192881717</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192914485</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192947253</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192980021</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766193012789</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766193045557</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192554037</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192586805</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192619573</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192652341</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192685109</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31766192717877</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31769668321333</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes?variant=31769668452405</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31766306062389</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes?variant=31766306095157</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=42960350609461</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://insulation4less.co.uk/products/recticel-eurowall-full-fill-cavity?variant=42960350642229</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes.json</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-cavitywall-1-2m-x-0-45m-all-sizes.json</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurothane-pl-2-4m-x-1-2m-all-sizes.json</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://build4less.co.uk/products/recticel-eurowall-full-fill-cavity.json</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625999744</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626032512</t>
-  </si>
-  <si>
     <t>N/L</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626098048</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626130816</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626163584</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626196352</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597626229120</t>
-  </si>
-  <si>
     <t>£39.80</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625901440</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625934208</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurothane-gp-insulation-board-1200-x-2400mm?variant=55597625966976</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286930304</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286963072</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.building-supplies-online.co.uk/products/recticel-eurowall-full-fill-cavity?variant=55598286995840</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-25mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-30mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-40mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-50mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-60mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-70mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-75mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-80mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-90mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-100mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-110mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-120mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-130mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-140mm.html</t>
-  </si>
-  <si>
-    <t>Error: 403 Client Error: Forbidden for url: https://www.insulationsuperstore.co.uk/product/recticel-eurothane-general-purpose-pir-insulation-board-2400-x-1200-x-150mm.html</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/25mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/30mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/40mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/50mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/60mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/70mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/75mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/80mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/90mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/100mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/110mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/120mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/130mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/140mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/150mm-recticel-eurothane-gp-pir-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/50mm-recticel-eurowall-partial-fill-cavity-insulation-board-1200mm-x-450mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/100mm-recticel-eurowall-partial-fill-cavity-insulation-board-1200mm-x-450mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/90mm-recticel-eurowall-full-fill-cavity-wall-insulation-1200mm-x-460mm</t>
-  </si>
-  <si>
     <t>£703.35</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://www.insulationuk.co.uk/products/140mm-recticel-eurowall-full-fill-cavity-wall-insulation-1200mm-x-460mm</t>
-  </si>
-  <si>
     <t>£15.38</t>
   </si>
   <si>
@@ -547,35 +331,6 @@
     <t>£26.28</t>
   </si>
   <si>
-    <t xml:space="preserve">Error: Message: element click intercepted: Element &lt;select name="super_attribute[1999]" id="attribute1999" class="form-select super-attribute-select max-w-full" x-on:change="changeOption(1999, event.target.value)" required=""&gt;...&lt;/select&gt; is not clickable at point (457, 837). Other element would receive the click: &lt;button type="button" class="btn btn-primary gap-2" data-role="cta"&gt;...&lt;/button&gt;
-  (Session info: chrome=150.0.7871.187); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#elementclickinterceptedexception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6e05a0d25+155a5]
-	chromedriver!GetHandleVerifier [0x7ff6e05a0d80+15600]
-	chromedriver!(No symbol) [0x7ff6e00f594d]
-	chromedriver!(No symbol) [0x7ff6e0158575]
-	chromedriver!(No symbol) [0x7ff6e0156193]
-	chromedriver!(No symbol) [0x7ff6e01534e7]
-	chromedriver!(No symbol) [0x7ff6e01523a0]
-	chromedriver!(No symbol) [0x7ff6e0144d98]
-	chromedriver!(No symbol) [0x7ff6e01791ca]
-	chromedriver!(No symbol) [0x7ff6e0144616]
-	chromedriver!(No symbol) [0x7ff6e019e01b]
-	chromedriver!(No symbol) [0x7ff6e0142e6c]
-	chromedriver!(No symbol) [0x7ff6e0143d93]
-	chromedriver!GetHandleVerifier [0x7ff6e0b86431+5facb1]
-	chromedriver!GetHandleVerifier [0x7ff6e0b80a9b+5f531b]
-	chromedriver!GetHandleVerifier [0x7ff6e0ba5865+61a0e5]
-	chromedriver!GetHandleVerifier [0x7ff6e05bdace+3234e]
-	chromedriver!GetHandleVerifier [0x7ff6e05c661c+3ae9c]
-	chromedriver!GetHandleVerifier [0x7ff6e05aab74+1f3f4]
-	chromedriver!GetHandleVerifier [0x7ff6e05aad04+1f584]
-	chromedriver!GetHandleVerifier [0x7ff6e058d9d7+2257]
-	KERNEL32!BaseThreadInitThunk [0x7ffe9eb7e957+17]
-	ntdll!RtlUserThreadStart [0x7ffea0ecad6c+2c]
-</t>
-  </si>
-  <si>
     <t>£36.62</t>
   </si>
   <si>
@@ -705,51 +460,12 @@
     <t>£23.13</t>
   </si>
   <si>
-    <t>£19.27</t>
-  </si>
-  <si>
-    <t>£20.83</t>
-  </si>
-  <si>
-    <t>£24.26</t>
-  </si>
-  <si>
-    <t>£27.59</t>
-  </si>
-  <si>
-    <t>£31.06</t>
-  </si>
-  <si>
-    <t>£40.83</t>
-  </si>
-  <si>
-    <t>£43.06</t>
-  </si>
-  <si>
-    <t>£55.70</t>
-  </si>
-  <si>
-    <t>£74.88</t>
-  </si>
-  <si>
-    <t>£66.58</t>
-  </si>
-  <si>
-    <t>£78.08</t>
-  </si>
-  <si>
     <t>£126.96</t>
   </si>
   <si>
     <t>£122.43</t>
   </si>
   <si>
-    <t>£446.12</t>
-  </si>
-  <si>
-    <t>£356.90</t>
-  </si>
-  <si>
     <t>£15.25</t>
   </si>
   <si>
@@ -852,62 +568,251 @@
     <t>£57.57</t>
   </si>
   <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/25mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/30mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/40mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/50mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/60mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/70mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/75mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/80mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/90mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/100mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/120mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/150mm-recticel-eurothane-insulation-board-2400mm-x-1200mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/50mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/products/100mm-recticel-eurowall-cavity-wall-insulation-board-1200mm-x-450mm</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/90mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/115mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
-  </si>
-  <si>
-    <t>Error: 429 Client Error: Too Many Requests for url: https://diybuildingsupplies.co.uk/collections/recticel-insulation/products/140mm-recticel-eurowall-plus-full-fill-cavity-insulation-board</t>
+    <t>£17.84</t>
+  </si>
+  <si>
+    <t>£23.15</t>
+  </si>
+  <si>
+    <t>£29.55</t>
+  </si>
+  <si>
+    <t>£32.52</t>
+  </si>
+  <si>
+    <t>£32.75</t>
+  </si>
+  <si>
+    <t>£36.18</t>
+  </si>
+  <si>
+    <t>£39.65</t>
+  </si>
+  <si>
+    <t>£48.66</t>
+  </si>
+  <si>
+    <t>£49.35</t>
+  </si>
+  <si>
+    <t>£58.94</t>
+  </si>
+  <si>
+    <t>£59.99</t>
+  </si>
+  <si>
+    <t>£59.45</t>
+  </si>
+  <si>
+    <t>£276.59</t>
+  </si>
+  <si>
+    <t>£126.47</t>
+  </si>
+  <si>
+    <t>£111.78</t>
+  </si>
+  <si>
+    <t>£41.50</t>
+  </si>
+  <si>
+    <t>£51.64</t>
+  </si>
+  <si>
+    <t>£55.32</t>
+  </si>
+  <si>
+    <t>£786.50</t>
+  </si>
+  <si>
+    <t>£791.80</t>
+  </si>
+  <si>
+    <t>£15.50</t>
+  </si>
+  <si>
+    <t>£17.99</t>
+  </si>
+  <si>
+    <t>£36.45</t>
+  </si>
+  <si>
+    <t>£59.02</t>
+  </si>
+  <si>
+    <t>£58.97</t>
+  </si>
+  <si>
+    <t>£206.12</t>
+  </si>
+  <si>
+    <t>£182.51</t>
+  </si>
+  <si>
+    <t>£626.65</t>
+  </si>
+  <si>
+    <t>£728.0</t>
+  </si>
+  <si>
+    <t>£17.75</t>
+  </si>
+  <si>
+    <t>£21.50</t>
+  </si>
+  <si>
+    <t>£23.25</t>
+  </si>
+  <si>
+    <t>£27.75</t>
+  </si>
+  <si>
+    <t>£31.50</t>
+  </si>
+  <si>
+    <t>£31.75</t>
+  </si>
+  <si>
+    <t>£35.25</t>
+  </si>
+  <si>
+    <t>£38.25</t>
+  </si>
+  <si>
+    <t>£39.75</t>
+  </si>
+  <si>
+    <t>£47.00</t>
+  </si>
+  <si>
+    <t>£48.75</t>
+  </si>
+  <si>
+    <t>£56.50</t>
+  </si>
+  <si>
+    <t>£59.75</t>
+  </si>
+  <si>
+    <t>£58.25</t>
+  </si>
+  <si>
+    <t>£31.96</t>
+  </si>
+  <si>
+    <t>£48.18</t>
+  </si>
+  <si>
+    <t>£72.71</t>
+  </si>
+  <si>
+    <t>£83.24</t>
+  </si>
+  <si>
+    <t>£90.28</t>
+  </si>
+  <si>
+    <t>£101.46</t>
+  </si>
+  <si>
+    <t>£114.31</t>
+  </si>
+  <si>
+    <t>£16.67</t>
+  </si>
+  <si>
+    <t>£19.49</t>
+  </si>
+  <si>
+    <t>£24.85</t>
+  </si>
+  <si>
+    <t>£25.82</t>
+  </si>
+  <si>
+    <t>£31.54</t>
+  </si>
+  <si>
+    <t>£36.34</t>
+  </si>
+  <si>
+    <t>£35.03</t>
+  </si>
+  <si>
+    <t>£39.38</t>
+  </si>
+  <si>
+    <t>£44.47</t>
+  </si>
+  <si>
+    <t>£43.77</t>
+  </si>
+  <si>
+    <t>£54.40</t>
+  </si>
+  <si>
+    <t>£66.42</t>
+  </si>
+  <si>
+    <t>£117.43</t>
+  </si>
+  <si>
+    <t>£203.51</t>
+  </si>
+  <si>
+    <t>£848.7</t>
+  </si>
+  <si>
+    <t>£908.35</t>
+  </si>
+  <si>
+    <t>£1156.54</t>
+  </si>
+  <si>
+    <t>£25.00</t>
+  </si>
+  <si>
+    <t>£29.11</t>
+  </si>
+  <si>
+    <t>£33.11</t>
+  </si>
+  <si>
+    <t>£37.27</t>
+  </si>
+  <si>
+    <t>£48.99</t>
+  </si>
+  <si>
+    <t>£51.67</t>
+  </si>
+  <si>
+    <t>£66.84</t>
+  </si>
+  <si>
+    <t>£79.89</t>
+  </si>
+  <si>
+    <t>£89.86</t>
+  </si>
+  <si>
+    <t>£93.69</t>
+  </si>
+  <si>
+    <t>£99.37</t>
+  </si>
+  <si>
+    <t>£657.00</t>
+  </si>
+  <si>
+    <t>£711.4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -970,13 +875,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1014,7 +927,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1048,6 +961,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1082,9 +996,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1257,11 +1172,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1317,7 +1232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1325,55 +1240,55 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="F2" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="G2" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="H2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" t="s">
+        <v>129</v>
+      </c>
+      <c r="N2" t="s">
+        <v>145</v>
+      </c>
+      <c r="O2" t="s">
+        <v>148</v>
+      </c>
+      <c r="P2" t="s">
         <v>144</v>
       </c>
-      <c r="I2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K2" t="s">
-        <v>188</v>
-      </c>
-      <c r="L2" t="s">
-        <v>96</v>
-      </c>
-      <c r="M2" t="s">
-        <v>204</v>
-      </c>
-      <c r="N2" t="s">
-        <v>220</v>
-      </c>
-      <c r="O2" t="s">
-        <v>236</v>
-      </c>
-      <c r="P2" t="s">
-        <v>219</v>
-      </c>
       <c r="Q2" t="s">
-        <v>256</v>
+        <v>168</v>
       </c>
       <c r="R2" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1381,55 +1296,55 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>182</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="H3" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="J3" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="L3" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M3" t="s">
-        <v>205</v>
+        <v>130</v>
       </c>
       <c r="N3" t="s">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="O3" t="s">
-        <v>237</v>
+        <v>149</v>
       </c>
       <c r="P3" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q3" t="s">
-        <v>257</v>
+        <v>169</v>
       </c>
       <c r="R3" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1437,55 +1352,55 @@
         <v>44</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>170</v>
       </c>
       <c r="H4" t="s">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
       <c r="J4" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="K4" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="L4" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M4" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="N4" t="s">
-        <v>222</v>
+        <v>250</v>
       </c>
       <c r="O4" t="s">
-        <v>238</v>
+        <v>150</v>
       </c>
       <c r="P4" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q4" t="s">
-        <v>258</v>
+        <v>170</v>
       </c>
       <c r="R4" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1493,55 +1408,55 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="F5" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="G5" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s">
-        <v>178</v>
+        <v>103</v>
       </c>
       <c r="K5" t="s">
-        <v>191</v>
+        <v>116</v>
       </c>
       <c r="L5" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M5" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="N5" t="s">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="O5" t="s">
-        <v>239</v>
+        <v>151</v>
       </c>
       <c r="P5" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q5" t="s">
-        <v>259</v>
+        <v>171</v>
       </c>
       <c r="R5" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1549,55 +1464,55 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" t="s">
+        <v>172</v>
+      </c>
+      <c r="H6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" t="s">
         <v>90</v>
       </c>
-      <c r="E6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I6" t="s">
-        <v>164</v>
-      </c>
       <c r="J6" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="K6" t="s">
-        <v>192</v>
+        <v>117</v>
       </c>
       <c r="L6" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M6" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="N6" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="O6" t="s">
-        <v>240</v>
+        <v>152</v>
       </c>
       <c r="P6" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q6" t="s">
-        <v>260</v>
+        <v>172</v>
       </c>
       <c r="R6" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1605,55 +1520,55 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="E7" t="s">
-        <v>99</v>
+        <v>185</v>
       </c>
       <c r="F7" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="G7" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="H7" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="I7" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="J7" t="s">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="K7" t="s">
-        <v>193</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M7" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="N7" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="O7" t="s">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="P7" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q7" t="s">
-        <v>261</v>
+        <v>173</v>
       </c>
       <c r="R7" t="s">
-        <v>275</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1661,55 +1576,55 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>186</v>
       </c>
       <c r="F8" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="G8" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="H8" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="K8" t="s">
-        <v>194</v>
+        <v>119</v>
       </c>
       <c r="L8" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M8" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="O8" t="s">
-        <v>242</v>
+        <v>154</v>
       </c>
       <c r="P8" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q8" t="s">
-        <v>242</v>
+        <v>154</v>
       </c>
       <c r="R8" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1717,55 +1632,55 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="F9" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="G9" t="s">
-        <v>131</v>
+        <v>204</v>
       </c>
       <c r="H9" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
       <c r="I9" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="J9" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="K9" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="L9" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M9" t="s">
-        <v>211</v>
+        <v>136</v>
       </c>
       <c r="N9" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="O9" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="P9" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q9" t="s">
-        <v>262</v>
+        <v>174</v>
       </c>
       <c r="R9" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1773,55 +1688,55 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="H10" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="I10" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="J10" t="s">
-        <v>182</v>
+        <v>107</v>
       </c>
       <c r="K10" t="s">
-        <v>195</v>
+        <v>120</v>
       </c>
       <c r="L10" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M10" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N10" t="s">
-        <v>227</v>
+        <v>144</v>
       </c>
       <c r="O10" t="s">
-        <v>244</v>
+        <v>156</v>
       </c>
       <c r="P10" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q10" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="R10" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1829,55 +1744,55 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="E11" t="s">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="F11" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="G11" t="s">
-        <v>133</v>
+        <v>188</v>
       </c>
       <c r="H11" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
       <c r="J11" t="s">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c r="K11" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M11" t="s">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N11" t="s">
-        <v>227</v>
+        <v>255</v>
       </c>
       <c r="O11" t="s">
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="P11" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q11" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="R11" t="s">
-        <v>279</v>
+        <v>241</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1885,55 +1800,55 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
       <c r="E12" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G12" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" t="s">
         <v>96</v>
       </c>
-      <c r="F12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G12" t="s">
-        <v>134</v>
-      </c>
-      <c r="H12" t="s">
-        <v>96</v>
-      </c>
-      <c r="I12" t="s">
-        <v>170</v>
-      </c>
       <c r="J12" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" t="s">
+        <v>144</v>
+      </c>
+      <c r="O12" t="s">
+        <v>158</v>
+      </c>
+      <c r="P12" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q12" t="s">
         <v>177</v>
       </c>
-      <c r="K12" t="s">
-        <v>96</v>
-      </c>
-      <c r="L12" t="s">
-        <v>96</v>
-      </c>
-      <c r="M12" t="s">
-        <v>213</v>
-      </c>
-      <c r="N12" t="s">
-        <v>228</v>
-      </c>
-      <c r="O12" t="s">
-        <v>246</v>
-      </c>
-      <c r="P12" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>265</v>
-      </c>
       <c r="R12" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1941,55 +1856,55 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="E13" t="s">
-        <v>104</v>
+        <v>190</v>
       </c>
       <c r="F13" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="G13" t="s">
-        <v>135</v>
+        <v>178</v>
       </c>
       <c r="H13" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="I13" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>177</v>
+        <v>227</v>
       </c>
       <c r="K13" t="s">
-        <v>197</v>
+        <v>122</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M13" t="s">
-        <v>214</v>
+        <v>139</v>
       </c>
       <c r="N13" t="s">
-        <v>228</v>
+        <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>247</v>
+        <v>159</v>
       </c>
       <c r="P13" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q13" t="s">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="R13" t="s">
-        <v>280</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1997,55 +1912,55 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
+        <v>205</v>
       </c>
       <c r="H14" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>177</v>
+        <v>228</v>
       </c>
       <c r="K14" t="s">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M14" t="s">
-        <v>215</v>
+        <v>140</v>
       </c>
       <c r="N14" t="s">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="O14" t="s">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="P14" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q14" t="s">
-        <v>267</v>
+        <v>179</v>
       </c>
       <c r="R14" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2053,55 +1968,55 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="E15" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="G15" t="s">
-        <v>137</v>
+        <v>192</v>
       </c>
       <c r="H15" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="I15" t="s">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="J15" t="s">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="K15" t="s">
-        <v>199</v>
+        <v>124</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M15" t="s">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="N15" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="O15" t="s">
-        <v>249</v>
+        <v>161</v>
       </c>
       <c r="P15" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q15" t="s">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="R15" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2109,55 +2024,55 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="E16" t="s">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="F16" t="s">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="G16" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="H16" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="K16" t="s">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M16" t="s">
-        <v>217</v>
+        <v>142</v>
       </c>
       <c r="N16" t="s">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="O16" t="s">
-        <v>250</v>
+        <v>162</v>
       </c>
       <c r="P16" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q16" t="s">
-        <v>269</v>
+        <v>181</v>
       </c>
       <c r="R16" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -2165,55 +2080,55 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="K17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="L17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="O17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="P17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="Q17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R17" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -2221,55 +2136,55 @@
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J18" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="K18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="L18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N18" t="s">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="O18" t="s">
-        <v>251</v>
+        <v>163</v>
       </c>
       <c r="P18" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q18" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R18" t="s">
-        <v>282</v>
+        <v>244</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -2277,55 +2192,55 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G19" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="H19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J19" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="K19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="L19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>233</v>
+        <v>147</v>
       </c>
       <c r="O19" t="s">
-        <v>252</v>
+        <v>164</v>
       </c>
       <c r="P19" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="Q19" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R19" t="s">
-        <v>283</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -2333,55 +2248,55 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J20" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="K20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="L20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="O20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="P20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="Q20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R20" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -2389,55 +2304,55 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J21" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="K21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="L21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="O21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="P21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="Q21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R21" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -2445,55 +2360,55 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>199</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>199</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="I22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J22" t="s">
-        <v>187</v>
+        <v>112</v>
       </c>
       <c r="K22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="L22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="N22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="O22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="P22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="Q22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R22" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2501,55 +2416,55 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>200</v>
       </c>
       <c r="E23" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="H23" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="I23" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J23" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="K23" t="s">
-        <v>201</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M23" t="s">
-        <v>218</v>
+        <v>143</v>
       </c>
       <c r="N23" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="O23" t="s">
-        <v>253</v>
+        <v>165</v>
       </c>
       <c r="P23" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="Q23" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R23" t="s">
-        <v>284</v>
+        <v>246</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2557,55 +2472,55 @@
         <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>200</v>
       </c>
       <c r="F24" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G24" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="H24" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
       <c r="I24" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J24" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="K24" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M24" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="N24" t="s">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s">
-        <v>254</v>
+        <v>166</v>
       </c>
       <c r="P24" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="Q24" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R24" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -2613,52 +2528,52 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>201</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="E25" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="F25" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="H25" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="J25" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="K25" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="M25" t="s">
-        <v>219</v>
+        <v>144</v>
       </c>
       <c r="N25" t="s">
-        <v>235</v>
+        <v>261</v>
       </c>
       <c r="O25" t="s">
-        <v>255</v>
+        <v>167</v>
       </c>
       <c r="P25" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="Q25" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="R25" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_03-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286A6C96-0363-495F-A2B2-213AC530EB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F948550-CDD3-48E3-8676-FD0285F40490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33870" yWindow="1710" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35250" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -400,12 +400,6 @@
     <t>£69.02</t>
   </si>
   <si>
-    <t>£141.19</t>
-  </si>
-  <si>
-    <t>£143.21</t>
-  </si>
-  <si>
     <t>£678.81</t>
   </si>
   <si>
@@ -806,6 +800,12 @@
   </si>
   <si>
     <t>£711.4</t>
+  </si>
+  <si>
+    <t>£705.95</t>
+  </si>
+  <si>
+    <t>£716.05</t>
   </si>
 </sst>
 </file>
@@ -1240,19 +1240,19 @@
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H2" t="s">
         <v>70</v>
@@ -1270,22 +1270,22 @@
         <v>67</v>
       </c>
       <c r="M2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="O2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="R2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1296,19 +1296,19 @@
         <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H3" t="s">
         <v>71</v>
@@ -1326,22 +1326,22 @@
         <v>67</v>
       </c>
       <c r="M3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1361,10 +1361,10 @@
         <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H4" t="s">
         <v>72</v>
@@ -1373,7 +1373,7 @@
         <v>88</v>
       </c>
       <c r="J4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K4" t="s">
         <v>115</v>
@@ -1382,22 +1382,22 @@
         <v>67</v>
       </c>
       <c r="M4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="O4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="P4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="R4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1408,19 +1408,19 @@
         <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="H5" t="s">
         <v>73</v>
@@ -1438,22 +1438,22 @@
         <v>67</v>
       </c>
       <c r="M5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="O5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="P5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1464,19 +1464,19 @@
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H6" t="s">
         <v>74</v>
@@ -1494,22 +1494,22 @@
         <v>67</v>
       </c>
       <c r="M6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1520,19 +1520,19 @@
         <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H7" t="s">
         <v>75</v>
@@ -1550,22 +1550,22 @@
         <v>67</v>
       </c>
       <c r="M7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="P7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="R7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1576,19 +1576,19 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
         <v>75</v>
@@ -1597,7 +1597,7 @@
         <v>92</v>
       </c>
       <c r="J8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K8" t="s">
         <v>119</v>
@@ -1606,22 +1606,22 @@
         <v>67</v>
       </c>
       <c r="M8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="O8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R8" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1632,19 +1632,19 @@
         <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H9" t="s">
         <v>76</v>
@@ -1662,22 +1662,22 @@
         <v>67</v>
       </c>
       <c r="M9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="O9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="P9" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1697,10 +1697,10 @@
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H10" t="s">
         <v>77</v>
@@ -1721,19 +1721,19 @@
         <v>67</v>
       </c>
       <c r="N10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="R10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1744,19 +1744,19 @@
         <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H11" t="s">
         <v>78</v>
@@ -1774,22 +1774,22 @@
         <v>67</v>
       </c>
       <c r="M11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="O11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R11" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1800,19 +1800,19 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D12" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E12" t="s">
         <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H12" t="s">
         <v>67</v>
@@ -1830,19 +1830,19 @@
         <v>67</v>
       </c>
       <c r="M12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="O12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R12" t="s">
         <v>67</v>
@@ -1856,19 +1856,19 @@
         <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H13" t="s">
         <v>79</v>
@@ -1877,7 +1877,7 @@
         <v>97</v>
       </c>
       <c r="J13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K13" t="s">
         <v>122</v>
@@ -1886,22 +1886,22 @@
         <v>67</v>
       </c>
       <c r="M13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="P13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="R13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1912,19 +1912,19 @@
         <v>54</v>
       </c>
       <c r="C14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E14" t="s">
         <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H14" t="s">
         <v>80</v>
@@ -1933,7 +1933,7 @@
         <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K14" t="s">
         <v>123</v>
@@ -1942,19 +1942,19 @@
         <v>67</v>
       </c>
       <c r="M14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N14" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="O14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q14" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R14" t="s">
         <v>67</v>
@@ -1968,19 +1968,19 @@
         <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E15" t="s">
         <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G15" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H15" t="s">
         <v>81</v>
@@ -1998,19 +1998,19 @@
         <v>67</v>
       </c>
       <c r="M15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="P15" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q15" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R15" t="s">
         <v>67</v>
@@ -2024,19 +2024,19 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F16" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G16" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H16" t="s">
         <v>82</v>
@@ -2045,7 +2045,7 @@
         <v>100</v>
       </c>
       <c r="J16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K16" t="s">
         <v>125</v>
@@ -2054,22 +2054,22 @@
         <v>67</v>
       </c>
       <c r="M16" t="s">
+        <v>140</v>
+      </c>
+      <c r="N16" t="s">
+        <v>257</v>
+      </c>
+      <c r="O16" t="s">
+        <v>160</v>
+      </c>
+      <c r="P16" t="s">
         <v>142</v>
       </c>
-      <c r="N16" t="s">
-        <v>259</v>
-      </c>
-      <c r="O16" t="s">
-        <v>162</v>
-      </c>
-      <c r="P16" t="s">
-        <v>144</v>
-      </c>
       <c r="Q16" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R16" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D17" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E17" t="s">
         <v>67</v>
@@ -2136,10 +2136,10 @@
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D18" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E18" t="s">
         <v>67</v>
@@ -2148,7 +2148,7 @@
         <v>67</v>
       </c>
       <c r="G18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H18" t="s">
         <v>67</v>
@@ -2169,19 +2169,19 @@
         <v>67</v>
       </c>
       <c r="N18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="O18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q18" t="s">
         <v>67</v>
       </c>
       <c r="R18" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
@@ -2192,10 +2192,10 @@
         <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D19" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E19" t="s">
         <v>67</v>
@@ -2204,7 +2204,7 @@
         <v>67</v>
       </c>
       <c r="G19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H19" t="s">
         <v>67</v>
@@ -2225,19 +2225,19 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O19" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q19" t="s">
         <v>67</v>
       </c>
       <c r="R19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2248,10 +2248,10 @@
         <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E20" t="s">
         <v>67</v>
@@ -2269,7 +2269,7 @@
         <v>67</v>
       </c>
       <c r="J20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K20" t="s">
         <v>67</v>
@@ -2304,10 +2304,10 @@
         <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E21" t="s">
         <v>67</v>
@@ -2325,7 +2325,7 @@
         <v>67</v>
       </c>
       <c r="J21" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K21" t="s">
         <v>67</v>
@@ -2360,10 +2360,10 @@
         <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s">
         <v>67</v>
@@ -2416,19 +2416,19 @@
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E23" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F23" t="s">
         <v>67</v>
       </c>
       <c r="G23" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H23" t="s">
         <v>83</v>
@@ -2440,19 +2440,19 @@
         <v>67</v>
       </c>
       <c r="K23" t="s">
-        <v>126</v>
+        <v>260</v>
       </c>
       <c r="L23" t="s">
         <v>67</v>
       </c>
       <c r="M23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P23" t="s">
         <v>67</v>
@@ -2461,7 +2461,7 @@
         <v>67</v>
       </c>
       <c r="R23" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2472,13 +2472,13 @@
         <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F24" t="s">
         <v>67</v>
@@ -2496,19 +2496,19 @@
         <v>67</v>
       </c>
       <c r="K24" t="s">
-        <v>127</v>
+        <v>261</v>
       </c>
       <c r="L24" t="s">
         <v>67</v>
       </c>
       <c r="M24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="O24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="P24" t="s">
         <v>67</v>
@@ -2517,7 +2517,7 @@
         <v>67</v>
       </c>
       <c r="R24" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2528,19 +2528,19 @@
         <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F25" t="s">
         <v>67</v>
       </c>
       <c r="G25" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H25" t="s">
         <v>85</v>
@@ -2552,19 +2552,19 @@
         <v>67</v>
       </c>
       <c r="K25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="L25" t="s">
         <v>67</v>
       </c>
       <c r="M25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P25" t="s">
         <v>67</v>
@@ -2573,7 +2573,7 @@
         <v>67</v>
       </c>
       <c r="R25" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
